--- a/e2e/fixtures/import/servicios-import-mixto.xlsx
+++ b/e2e/fixtures/import/servicios-import-mixto.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Precio Cero</t>
+          <t>Precio Negativo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
